--- a/trading_journal_v2.xlsx
+++ b/trading_journal_v2.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -522,12 +522,16 @@
         <v>80.16</v>
       </c>
       <c r="I2" t="n">
-        <v>44.64</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+        <v>44.71</v>
+      </c>
+      <c r="J2" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="K2" t="n">
+        <v>11.55</v>
+      </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>9.26</v>
       </c>
     </row>
     <row r="3">
@@ -562,12 +566,14 @@
         <v>91.8</v>
       </c>
       <c r="I3" t="n">
-        <v>16.82</v>
+        <v>16.78</v>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>9.67</v>
+      </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -592,17 +598,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>66.12</v>
       </c>
       <c r="I4" t="n">
-        <v>50.82</v>
+        <v>50.63</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -642,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>236.41</v>
+        <v>235.72</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -682,7 +688,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>232.63</v>
+        <v>231.94</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -722,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>11.23</v>
+        <v>11.27</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -762,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>39.78</v>
+        <v>39.85</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -802,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>33.78</v>
+        <v>33.81</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -842,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>251.18</v>
+        <v>250.98</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -882,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>68.37</v>
+        <v>68.63</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -922,7 +928,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>76.20999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -952,7 +958,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -962,12 +968,16 @@
         <v>23</v>
       </c>
       <c r="I13" t="n">
-        <v>112.04</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+        <v>112.71</v>
+      </c>
+      <c r="J13" t="n">
+        <v>112.71</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1860.17</v>
+      </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>427.84</v>
       </c>
     </row>
     <row r="14">
@@ -992,17 +1002,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>312.9</v>
       </c>
       <c r="I14" t="n">
-        <v>52.31</v>
+        <v>52.47</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>

--- a/trading_journal_v2.xlsx
+++ b/trading_journal_v2.xlsx
@@ -566,14 +566,14 @@
         <v>91.8</v>
       </c>
       <c r="I3" t="n">
-        <v>16.78</v>
+        <v>16.79</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>9.67</v>
+        <v>9.74</v>
       </c>
       <c r="L3" t="n">
-        <v>8.880000000000001</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="4">
@@ -598,7 +598,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -610,10 +610,14 @@
       <c r="I4" t="n">
         <v>50.63</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>50.63</v>
+      </c>
+      <c r="K4" t="n">
+        <v>53.15</v>
+      </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="5">
@@ -638,17 +642,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>229.4</v>
       </c>
       <c r="I5" t="n">
-        <v>235.72</v>
+        <v>236.19</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -688,7 +692,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>231.94</v>
+        <v>231.79</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -728,7 +732,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>11.27</v>
+        <v>11.34</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -768,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>39.85</v>
+        <v>39.84</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -808,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>33.81</v>
+        <v>33.72</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -848,7 +852,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>250.98</v>
+        <v>251.15</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -888,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>68.63</v>
+        <v>68.5</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -928,7 +932,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>76.3</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1012,12 +1016,14 @@
         <v>312.9</v>
       </c>
       <c r="I14" t="n">
-        <v>52.47</v>
+        <v>52.52</v>
       </c>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>0.71</v>
+      </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
     </row>
   </sheetData>

--- a/trading_journal_v2.xlsx
+++ b/trading_journal_v2.xlsx
@@ -566,14 +566,14 @@
         <v>91.8</v>
       </c>
       <c r="I3" t="n">
-        <v>16.79</v>
+        <v>16.86</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>9.74</v>
+        <v>10.2</v>
       </c>
       <c r="L3" t="n">
-        <v>8.94</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -642,7 +642,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -652,12 +652,16 @@
         <v>229.4</v>
       </c>
       <c r="I5" t="n">
-        <v>236.19</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+        <v>223.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>223.7</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-2.48</v>
+      </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="6">
@@ -692,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>231.79</v>
+        <v>232.01</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -732,7 +736,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>11.34</v>
+        <v>11.49</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -772,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>39.84</v>
+        <v>40.15</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -812,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>33.72</v>
+        <v>33.7</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -842,17 +846,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>233.62</v>
       </c>
       <c r="I10" t="n">
-        <v>251.15</v>
+        <v>249.96</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -892,7 +896,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>68.5</v>
+        <v>68.11</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -932,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>76.26000000000001</v>
+        <v>75.44</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1016,14 +1020,14 @@
         <v>312.9</v>
       </c>
       <c r="I14" t="n">
-        <v>52.52</v>
+        <v>52.47</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="L14" t="n">
-        <v>2.22</v>
+        <v>1.92</v>
       </c>
     </row>
   </sheetData>

--- a/trading_journal_v2.xlsx
+++ b/trading_journal_v2.xlsx
@@ -846,7 +846,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -858,10 +858,14 @@
       <c r="I10" t="n">
         <v>249.96</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>249.96</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.99</v>
+      </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="11">
@@ -886,14 +890,14 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="I11" t="n">
         <v>68.11</v>
